--- a/04_DESIGN_TABLES/DesignTable_6408_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6408_SW2.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-02-O built solid (OMi does not say hollow/solid here; ASSUMPTION)</t>
+          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-02-O built solid (OMi does not say hollow/solid here; ASSUMPTION) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.6~0.600; HEXB@HEX=0.44~0.438</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-03-O built solid (OMi does not say hollow/solid here; ASSUMPTION)</t>
+          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-03-O built solid (OMi does not say hollow/solid here; ASSUMPTION) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.6~0.600; HEXB@HEX=0.5~0.500</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-04-O = the cored plug (OMi sells the solid one separately as 6408-04-O-SLD; Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) - was DROP (no SKU match); replaces the Air-Way-less placeholder row 6408-04-O | HOLE DEPTH interpolated: ORB end 0.340 + 0.0133 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.3533; radial wall under the thread root / groove 0.082; with a 120deg drill point the head would keep 0.259 (Brennan: 0.220 at -08, 0.250 at -20)</t>
+          <t>BUILD 2026-09-25: OMi 6408-04-O = the cored plug (OMi sells the solid one separately as 6408-04-O-SLD; Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) - was DROP (no SKU match); replaces the Air-Way-less placeholder row 6408-04-O | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.67~0.670; HEXB@HEX=0.56~0.562; HOLE@BORE=0.2~0.205 | HOLE DEPTH interpolated: ORB end 0.340 + 0.0133 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.3533; radial wall under the thread root / groove 0.082; with a 120deg drill point the head would keep 0.259 (Brennan: 0.220 at -08, 0.250 at -20)</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>BUILD: OMi 6408-04-O-SLD (External Hex Plug Solid)</t>
+          <t>BUILD: OMi 6408-04-O-SLD (External Hex Plug Solid) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.67~0.670; HEXB@HEX=0.56~0.562</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-05-O built solid (OMi does not say hollow/solid here; ASSUMPTION)</t>
+          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-05-O built solid (OMi does not say hollow/solid here; ASSUMPTION) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.67~0.670; HEXB@HEX=0.63~0.625</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-12-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | HOLE DEPTH interpolated: ORB end 0.594 + 0.0267 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.6207; radial wall under the thread root / groove 0.142; with a 120deg drill point the head would keep 0.279 (Brennan: 0.220 at -08, 0.250 at -20)</t>
+          <t>BUILD 2026-09-25: OMi 6408-12-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.09~1.090; HEXB@HEX=1.25~1.250; HOLE@BORE=0.66~0.656 | HOLE DEPTH interpolated: ORB end 0.594 + 0.0267 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.6207; radial wall under the thread root / groove 0.142; with a 120deg drill point the head would keep 0.279 (Brennan: 0.220 at -08, 0.250 at -20)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>ORB -14 groove width MEASURED 0.125 on the Brennan 6400-14-14-O STEP (2026-09-25, single source)| BUILD 2026-09-25: OMi 6408-14-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | HOLE DEPTH interpolated: ORB end 0.594 + 0.0300 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.624; radial wall under the thread root / groove 0.175; with a 120deg drill point the head would keep 0.258 (Brennan: 0.220 at -08, 0.250 at -20)</t>
+          <t>ORB -14 groove width MEASURED 0.125 on the Brennan 6400-14-14-O STEP (2026-09-25, single source)| BUILD 2026-09-25: OMi 6408-14-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.09~1.090; HEXB@HEX=1.38~1.375; HOLE@BORE=0.72~0.718 | HOLE DEPTH interpolated: ORB end 0.594 + 0.0300 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.624; radial wall under the thread root / groove 0.175; with a 120deg drill point the head would keep 0.258 (Brennan: 0.220 at -08, 0.250 at -20)</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-20-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | Brennan 6408-20-O STEP: hole 1.093 (Air-Way 1.09), full diameter to 0.6345 from the tip (model 0.634), drill-point apex 0.950 -&gt; head wall 0.250; L 1.200, hex 1.875 (Air-Way 1.2 / 1.88)</t>
+          <t>BUILD 2026-09-25: OMi 6408-20-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.2~1.200; HEXB@HEX=1.88~1.875; HOLE@BORE=1.09~1.093 | Brennan 6408-20-O STEP: hole 1.093 (Air-Way 1.09), full diameter to 0.6345 from the tip (model 0.634), drill-point apex 0.950 -&gt; head wall 0.250; L 1.200, hex 1.875 (Air-Way 1.2 / 1.88)</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-24-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | HOLE DEPTH interpolated: ORB end 0.594 + 0.0467 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.6407; radial wall under the thread root / groove 0.208; with a 120deg drill point the head would keep 0.242 (Brennan: 0.220 at -08, 0.250 at -20)</t>
+          <t>BUILD 2026-09-25: OMi 6408-24-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.27~1.270; HEXB@HEX=2.13~2.125; HOLE@BORE=1.34~1.344 | HOLE DEPTH interpolated: ORB end 0.594 + 0.0467 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.6407; radial wall under the thread root / groove 0.208; with a 120deg drill point the head would keep 0.242 (Brennan: 0.220 at -08, 0.250 at -20)</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source)| BUILD 2026-09-25: OMi 6408-32-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | HOLE DEPTH interpolated: ORB end 0.594 + 0.0600 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.654; radial wall under the thread root / groove 0.285; with a 120deg drill point the head would keep 0.253 (Brennan: 0.220 at -08, 0.250 at -20)</t>
+          <t>ORB -32 groove width MEASURED 0.125 on the Brennan 6400-32-32-O STEP (2026-09-24, single source)| BUILD 2026-09-25: OMi 6408-32-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.43~1.430; HEXB@HEX=2.75~2.75; HOLE@BORE=1.81~1.813 | HOLE DEPTH interpolated: ORB end 0.594 + 0.0600 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.654; radial wall under the thread root / groove 0.285; with a 120deg drill point the head would keep 0.253 (Brennan: 0.220 at -08, 0.250 at -20)</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6408_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6408_SW2.xlsx
@@ -1585,7 +1585,7 @@
         <v>0.08333</v>
       </c>
       <c r="O12" t="n">
-        <v>0.874</v>
+        <v>0.88</v>
       </c>
       <c r="P12" t="n">
         <v>0.6273</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>ORB end: sourced (SAE J1926-4 plug); L/hex: Air-Way single source; HOLE@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1819 Side 1 ID = 0.874 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: ORB end: thread length + groove from the 6408 review table (SAE J1926 plug end; no tip chamfer modelled) - Brennan 6408-08-O / 6408-20-O STEPs: identical ORB ends; L / hex: Air-Way (Brennan -08 / -20 STEPs agree: L 0.800 / 1.200, hex 0.875 / 1.875); plug head = hex to a plain flat face (hex end chamfers not modelled); HOLLOW (-H) configs = the OMi 6408-xx-O cored plug: blind hole HOLE (Air-Way; Brennan 0.422 / 1.093) drilled from the ORB tip, full diameter to the ORB end length + 0.020 (-08) / 0.040 (-20) MEASURED on the Brennan STEPs, other sizes interpolated in proportion to the dash (ASSUMPTION); 120deg drill point not modelled; SOLID configs (-02/-03/-05: the only plug Air-Way lists there; -04: OMi 6408-04-O-SLD): hole feature suppressed</t>
+          <t>ORB end: sourced (SAE J1926-4 plug); L/hex: Air-Way single source; HOLE@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1819 Side 1 ID = 0.874 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; HOLE@BORE: Air-Way 0.88 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.874) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: ORB end: thread length + groove from the 6408 review table (SAE J1926 plug end; no tip chamfer modelled) - Brennan 6408-08-O / 6408-20-O STEPs: identical ORB ends; L / hex: Air-Way (Brennan -08 / -20 STEPs agree: L 0.800 / 1.200, hex 0.875 / 1.875); plug head = hex to a plain flat face (hex end chamfers not modelled); HOLLOW (-H) configs = the OMi 6408-xx-O cored plug: blind hole HOLE (Air-Way; Brennan 0.422 / 1.093) drilled from the ORB tip, full diameter to the ORB end length + 0.020 (-08) / 0.040 (-20) MEASURED on the Brennan STEPs, other sizes interpolated in proportion to the dash (ASSUMPTION); 120deg drill point not modelled; SOLID configs (-02/-03/-05: the only plug Air-Way lists there; -04: OMi 6408-04-O-SLD): hole feature suppressed</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-16-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | HOLE DEPTH interpolated: ORB end 0.594 + 0.0333 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.6273; radial wall under the thread root / groove 0.161; with a 120deg drill point the head would keep 0.240 (Brennan: 0.220 at -08, 0.250 at -20)</t>
+          <t>BUILD 2026-09-25: OMi 6408-16-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | 2026-10-20 Air-Way first: HOLE@BORE OMi/Brennan 0.874 -&gt; Air-Way 0.88 | HOLE DEPTH interpolated: ORB end 0.594 + 0.0333 (Brennan measured 0.020 at -08, 0.040 at -20) -&gt; 0.6273; radial wall under the thread root / groove 0.158; with a 120deg drill point the head would keep 0.239 (Brennan: 0.220 at -08, 0.250 at -20)</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
